--- a/e2e/fixtures/files/registry.xlsx
+++ b/e2e/fixtures/files/registry.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр договоров" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расчёт" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примечания" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Черновик" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,8 +59,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,373 +437,562 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Реестр действующих договоров на 15.01.2026</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Реестр действующих договоров ООО «Ромашка» на 2024 год</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Предмет</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Сумма, ₽</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Предмет договора</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Сроки</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Суммы, BYN</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ООО «Ромашка»</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Сопровождение</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>действует</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Сумма договора</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Оплачено</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ИП Иванов И. И.</t>
+          <t>ООО «Ромашка»</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Поставка</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>101250</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>продлён</t>
-        </is>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>01.01.2024</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>4800</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ООО «Василёк»</t>
+          <t>ИП Иванов И. И.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Аренда</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>102500</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>Поставка оборудования</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>02.02.2024</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04.12.2024</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6145</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3072.5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>На согласовании</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>АО «Одуванчик»</t>
+          <t>ООО «Василёк»</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>103750</v>
+          <t>Техническое обслуживание</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>03.03.2024</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>на подписании</t>
+          <t>07.12.2024</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>7490</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5617.5</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Завершён</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ООО «Клевер»</t>
+          <t>ЗАО «Тестовый Мост»</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Подряд</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>105000</v>
+          <t>Аренда помещения</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>04.04.2024</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>закрыт</t>
+          <t>10.12.2024</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>8835</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8835</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Продлён</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ООО «Ромашка»</t>
+          <t>ООО «ТехноСфера-Плюс»</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Сопровождение</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>106250</v>
+          <t>Консультационные услуги</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>05.05.2024</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>действует</t>
+          <t>13.12.2024</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>10180</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2545</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Расторгнут</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ИП Иванов И. И.</t>
+          <t>ОДО «Северный Ветер»</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Поставка</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>продлён</t>
+          <t>Подряд на монтаж</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>06.06.2024</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>11525</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5762.5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Действует</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ООО «Василёк»</t>
+          <t>ООО «Гранит-Строй»</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Аренда</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>108750</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>07.07.2024</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>19.12.2024</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>12870</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9652.5</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>На согласовании</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>АО «Одуванчик»</t>
+          <t>ООО «Ромашка»</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>110000</v>
+          <t>Поставка оборудования</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>08.08.2024</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>на подписании</t>
-        </is>
+          <t>22.12.2024</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>12710</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12710</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ООО «Клевер»</t>
+          <t>ИП Иванов И. И.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Подряд</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>111250</v>
+          <t>Техническое обслуживание</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>09.09.2024</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>закрыт</t>
+          <t>25.12.2024</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>14055</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3513.75</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Продлён</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ООО «Ромашка»</t>
+          <t>ООО «Василёк»</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Сопровождение</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>112500</v>
+          <t>Аренда помещения</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10.01.2024</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>действует</t>
+          <t>28.12.2024</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>15400</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7700</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Расторгнут</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ИП Иванов И. И.</t>
+          <t>ЗАО «Тестовый Мост»</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Поставка</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>113750</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>продлён</t>
+          <t>Консультационные услуги</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>11.02.2024</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>16745</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12558.75</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Действует</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ООО «Василёк»</t>
+          <t>ООО «ТехноСфера-Плюс»</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Аренда</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>115000</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Подряд на монтаж</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>12.03.2024</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>06.12.2024</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>18090</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>На согласовании</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>АО «Одуванчик»</t>
+          <t>ОДО «Северный Ветер»</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Консультации</t>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>13.04.2024</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>на подписании</t>
+          <t>09.12.2024</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>19435</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4858.75</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Завершён</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ООО «Клевер»</t>
+          <t>ООО «Гранит-Строй»</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Подряд</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>117500</v>
+          <t>Поставка оборудования</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>14.05.2024</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>закрыт</t>
+          <t>12.12.2024</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>20780</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10390</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Продлён</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -790,21 +1001,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Сопровождение</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>118750</v>
+          <t>Техническое обслуживание</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>15.06.2024</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>действует</t>
-        </is>
+          <t>15.12.2024</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>20620</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15465</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -813,21 +1032,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Поставка</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>продлён</t>
+          <t>Аренда помещения</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>16.07.2024</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>21965</v>
+      </c>
+      <c r="G20" t="n">
+        <v>21965</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Действует</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -836,510 +1063,846 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Аренда</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>121250</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Консультационные услуги</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>17.08.2024</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>21.12.2024</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>23310</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5827.5</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>На согласовании</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>АО «Одуванчик»</t>
+          <t>ЗАО «Тестовый Мост»</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>122500</v>
+          <t>Подряд на монтаж</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>18.09.2024</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>на подписании</t>
+          <t>24.12.2024</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>24655</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12327.5</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Завершён</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ООО «Клевер»</t>
+          <t>ООО «ТехноСфера-Плюс»</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Подряд</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>123750</v>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>19.01.2024</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>закрыт</t>
+          <t>27.12.2024</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>26000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19500</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Продлён</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ООО «Ромашка»</t>
+          <t>ОДО «Северный Ветер»</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Сопровождение</t>
+          <t>Поставка оборудования</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20.02.2024</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>действует</t>
+          <t>02.12.2024</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>27345</v>
+      </c>
+      <c r="G24" t="n">
+        <v>27345</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Расторгнут</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ИП Иванов И. И.</t>
+          <t>ООО «Гранит-Строй»</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Поставка</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>126250</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>продлён</t>
+          <t>Техническое обслуживание</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>21.03.2024</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>28690</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7172.5</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Действует</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ООО «Василёк»</t>
+          <t>ООО «Ромашка»</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Аренда</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>127500</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Аренда помещения</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>22.04.2024</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>08.12.2024</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>28530</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14265</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>АО «Одуванчик»</t>
+          <t>ИП Иванов И. И.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>128750</v>
+          <t>Консультационные услуги</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>23.05.2024</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>на подписании</t>
+          <t>11.12.2024</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>29875</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Завершён</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ООО «Клевер»</t>
+          <t>ООО «Василёк»</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Подряд</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>130000</v>
+          <t>Подряд на монтаж</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>24.06.2024</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>закрыт</t>
+          <t>14.12.2024</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>31220</v>
+      </c>
+      <c r="G28" t="n">
+        <v>31220</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Продлён</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ООО «Ромашка»</t>
+          <t>ЗАО «Тестовый Мост»</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Сопровождение</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>131250</v>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>25.07.2024</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>действует</t>
+          <t>17.12.2024</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>32565</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8141.25</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Расторгнут</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ИП Иванов И. И.</t>
+          <t>ООО «ТехноСфера-Плюс»</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Поставка</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>132500</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>продлён</t>
+          <t>Поставка оборудования</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>26.08.2024</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>33910</v>
+      </c>
+      <c r="G30" t="n">
+        <v>16955</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Действует</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ООО «Василёк»</t>
+          <t>ОДО «Северный Ветер»</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Аренда</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>Техническое обслуживание</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>27.09.2024</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>23.12.2024</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>35255</v>
+      </c>
+      <c r="G31" t="n">
+        <v>26441.25</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>На согласовании</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>АО «Одуванчик»</t>
+          <t>ООО «Гранит-Строй»</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>135000</v>
+          <t>Аренда помещения</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>28.01.2024</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>на подписании</t>
+          <t>26.12.2024</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>36600</v>
+      </c>
+      <c r="G32" t="n">
+        <v>36600</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Завершён</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ООО «Клевер»</t>
+          <t>ООО «Ромашка»</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Подряд</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>136250</v>
+          <t>Консультационные услуги</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>01.02.2024</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>закрыт</t>
-        </is>
+          <t>01.12.2024</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>36440</v>
+      </c>
+      <c r="G33" t="n">
+        <v>9110</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ООО «Ромашка»</t>
+          <t>ИП Иванов И. И.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Сопровождение</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>137500</v>
+          <t>Подряд на монтаж</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>02.03.2024</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>действует</t>
+          <t>04.12.2024</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>37785</v>
+      </c>
+      <c r="G34" t="n">
+        <v>18892.5</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Расторгнут</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ИП Иванов И. И.</t>
+          <t>ООО «Василёк»</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Поставка</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>138750</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>продлён</t>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>03.04.2024</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>39130</v>
+      </c>
+      <c r="G35" t="n">
+        <v>29347.5</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Действует</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ООО «Василёк»</t>
+          <t>ЗАО «Тестовый Мост»</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Аренда</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>Поставка оборудования</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>04.05.2024</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>10.12.2024</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>40475</v>
+      </c>
+      <c r="G36" t="n">
+        <v>40475</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>На согласовании</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>АО «Одуванчик»</t>
+          <t>ООО «ТехноСфера-Плюс»</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>141250</v>
+          <t>Техническое обслуживание</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>05.06.2024</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>на подписании</t>
+          <t>13.12.2024</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>41820</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10455</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Завершён</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ООО «Клевер»</t>
+          <t>ОДО «Северный Ветер»</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Подряд</t>
+          <t>Аренда помещения</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>06.07.2024</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>закрыт</t>
+          <t>16.12.2024</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>43165</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Продлён</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ООО «Ромашка»</t>
+          <t>ООО «Гранит-Строй»</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Сопровождение</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>143750</v>
+          <t>Консультационные услуги</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>07.08.2024</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>действует</t>
+          <t>19.12.2024</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>44510</v>
+      </c>
+      <c r="G39" t="n">
+        <v>33382.5</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Расторгнут</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ИП Иванов И. И.</t>
+          <t>ООО «Ромашка»</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Поставка</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>145000</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>продлён</t>
-        </is>
+          <t>Подряд на монтаж</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>08.09.2024</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>44350</v>
+      </c>
+      <c r="G40" t="n">
+        <v>44350</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ООО «Василёк»</t>
+          <t>ИП Иванов И. И.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Аренда</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>146250</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>Оказание услуг</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>09.01.2024</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>25.12.2024</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>45695</v>
+      </c>
+      <c r="G41" t="n">
+        <v>11423.75</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>На согласовании</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>АО «Одуванчик»</t>
+          <t>ООО «Василёк»</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>147500</v>
+          <t>Поставка оборудования</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10.02.2024</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>на подписании</t>
+          <t>28.12.2024</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>47040</v>
+      </c>
+      <c r="G42" t="n">
+        <v>23520</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Завершён</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ЗАО «Тестовый Мост»</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Техническое обслуживание</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>11.03.2024</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>03.12.2024</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>48385</v>
+      </c>
+      <c r="G43" t="n">
+        <v>36288.75</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Продлён</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
         <v>40</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ООО «Клевер»</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Подряд</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>148750</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>закрыт</t>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ООО «ТехноСфера-Плюс»</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Аренда помещения</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>12.04.2024</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>06.12.2024</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>49730</v>
+      </c>
+      <c r="G44" t="n">
+        <v>49730</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Расторгнут</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="D45">
-        <f>SUM(D4:D43)</f>
-        <v/>
+      <c r="F45" s="4" t="n">
+        <v>1098125</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>637416.25</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B45:C45"/>
+  <mergeCells count="8">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1351,61 +1914,151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ставка НДС</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.2</v>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Сводка по кварталам</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Сумма без НДС</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>250000</v>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Квартал</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>План, BYN</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Факт, BYN</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Отклонение</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Признак</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>НДС</t>
-        </is>
-      </c>
-      <c r="B4">
-        <f>B3*B2</f>
+          <t>1 квартал</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>58430.5</v>
+      </c>
+      <c r="D4">
+        <f>C4-B4</f>
+        <v>-1569.5</v>
+      </c>
+      <c r="E4">
+        <f>IF(C4&gt;=B4,"выполнен","не выполнен")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Итого с НДС</t>
-        </is>
-      </c>
-      <c r="B5">
-        <f>B3+B4</f>
+          <t>2 квартал</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>72000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>75120</v>
+      </c>
+      <c r="D5">
+        <f>C5-B5</f>
+        <v>3120</v>
+      </c>
+      <c r="E5">
+        <f>IF(C5&gt;=B5,"выполнен","не выполнен")</f>
         <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3 квартал</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>61004.25</v>
+      </c>
+      <c r="D6">
+        <f>C6-B6</f>
+        <v>-3995.75</v>
+      </c>
+      <c r="E6">
+        <f>IF(C6&gt;=B6,"выполнен","не выполнен")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4 квартал</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C7" t="n">
+        <v>79880.75</v>
+      </c>
+      <c r="D7">
+        <f>C7-B7</f>
+        <v>-119.25</v>
+      </c>
+      <c r="E7">
+        <f>IF(C7&gt;=B7,"выполнен","не выполнен")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>SUM(B4:B7)</f>
+        <v>277000</v>
+      </c>
+      <c r="C8">
+        <f>SUM(C4:C7)</f>
+        <v>274435.5</v>
+      </c>
+      <c r="D8">
+        <f>SUM(D4:D7)</f>
+        <v>-2564.5</v>
       </c>
     </row>
   </sheetData>
@@ -1419,13 +2072,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="B2:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Лист оставлен почти пустым намеренно.</t>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Лист намеренно оставлен почти пустым.</t>
         </is>
       </c>
     </row>
